--- a/BookDatabase.xlsx
+++ b/BookDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8522cc2110d77404/Documents/GitHub/ClearNotes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="448" documentId="11_F25DC773A252ABDACC10482A41D96DA65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E1ACEE-E8B5-4F37-9F94-22DE6FD850F5}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="11_F25DC773A252ABDACC10482A41D96DA65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C1E3721-1E72-40FA-9DE3-4A97D5846F02}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="460" windowWidth="19420" windowHeight="9730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="94">
   <si>
     <t>Class</t>
   </si>
@@ -295,6 +295,18 @@
   </si>
   <si>
     <t>ujp1</t>
+  </si>
+  <si>
+    <t>Importance</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Language</t>
   </si>
 </sst>
 </file>
@@ -345,12 +357,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -636,16 +645,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="19.26953125" customWidth="1"/>
     <col min="4" max="4" width="43.6328125" customWidth="1"/>
+    <col min="5" max="5" width="17.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,8 +668,11 @@
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -672,9 +685,12 @@
       <c r="D2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+      <c r="E2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -686,9 +702,12 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
+      <c r="E3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" t="s">
@@ -700,9 +719,12 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" t="s">
@@ -714,9 +736,12 @@
       <c r="D5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" t="s">
@@ -728,23 +753,29 @@
       <c r="D6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
+      <c r="E6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>26</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>2</v>
       </c>
       <c r="B8" t="s">
@@ -756,9 +787,12 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>2</v>
       </c>
       <c r="B9" t="s">
@@ -770,9 +804,12 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
+      <c r="E9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>3</v>
       </c>
       <c r="B10" t="s">
@@ -784,9 +821,12 @@
       <c r="D10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>3</v>
       </c>
       <c r="B11" t="s">
@@ -798,9 +838,12 @@
       <c r="D11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>3</v>
       </c>
       <c r="B12" t="s">
@@ -812,9 +855,12 @@
       <c r="D12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>3</v>
       </c>
       <c r="B13" t="s">
@@ -826,9 +872,12 @@
       <c r="D13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>3</v>
       </c>
       <c r="B14" t="s">
@@ -840,9 +889,12 @@
       <c r="D14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
+      <c r="E14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>3</v>
       </c>
       <c r="B15" t="s">
@@ -854,9 +906,12 @@
       <c r="D15" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
+      <c r="E15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>3</v>
       </c>
       <c r="B16" t="s">
@@ -868,9 +923,12 @@
       <c r="D16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>4</v>
       </c>
       <c r="B17" t="s">
@@ -882,9 +940,12 @@
       <c r="D17" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>4</v>
       </c>
       <c r="B18" t="s">
@@ -896,9 +957,12 @@
       <c r="D18" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
+      <c r="E18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>4</v>
       </c>
       <c r="B19" t="s">
@@ -910,9 +974,12 @@
       <c r="D19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="3">
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>4</v>
       </c>
       <c r="B20" t="s">
@@ -924,9 +991,12 @@
       <c r="D20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="3">
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>4</v>
       </c>
       <c r="B21" t="s">
@@ -938,9 +1008,12 @@
       <c r="D21" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
+      <c r="E21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>4</v>
       </c>
       <c r="B22" t="s">
@@ -952,9 +1025,12 @@
       <c r="D22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="3">
+      <c r="E22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>4</v>
       </c>
       <c r="B23" t="s">
@@ -966,9 +1042,12 @@
       <c r="D23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="3">
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>5</v>
       </c>
       <c r="B24" t="s">
@@ -980,9 +1059,12 @@
       <c r="D24" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>5</v>
       </c>
       <c r="B25" t="s">
@@ -994,9 +1076,12 @@
       <c r="D25" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="3">
+      <c r="E25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>5</v>
       </c>
       <c r="B26" t="s">
@@ -1008,9 +1093,12 @@
       <c r="D26" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="3">
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>5</v>
       </c>
       <c r="B27" t="s">
@@ -1022,9 +1110,12 @@
       <c r="D27" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="3">
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>5</v>
       </c>
       <c r="B28" t="s">
@@ -1036,9 +1127,12 @@
       <c r="D28" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="3">
+      <c r="E28" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>5</v>
       </c>
       <c r="B29" t="s">
@@ -1050,9 +1144,12 @@
       <c r="D29" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="3">
+      <c r="E29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>5</v>
       </c>
       <c r="B30" t="s">
@@ -1064,9 +1161,12 @@
       <c r="D30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
+      <c r="E30" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>6</v>
       </c>
       <c r="B31" t="s">
@@ -1078,9 +1178,12 @@
       <c r="D31" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="3">
+      <c r="E31" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>6</v>
       </c>
       <c r="B32" t="s">
@@ -1092,9 +1195,12 @@
       <c r="D32" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="3">
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>6</v>
       </c>
       <c r="B33" t="s">
@@ -1106,9 +1212,12 @@
       <c r="D33" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="3">
+      <c r="E33" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>6</v>
       </c>
       <c r="B34" t="s">
@@ -1120,9 +1229,12 @@
       <c r="D34" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="3">
+      <c r="E34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>6</v>
       </c>
       <c r="B35" t="s">
@@ -1134,9 +1246,12 @@
       <c r="D35" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="3">
+      <c r="E35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>6</v>
       </c>
       <c r="B36" t="s">
@@ -1148,9 +1263,12 @@
       <c r="D36" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="3">
+      <c r="E36" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>6</v>
       </c>
       <c r="B37" t="s">
@@ -1162,9 +1280,12 @@
       <c r="D37" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="3">
+      <c r="E37" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>6</v>
       </c>
       <c r="B38" t="s">
@@ -1176,9 +1297,12 @@
       <c r="D38" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="3">
+      <c r="E38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>6</v>
       </c>
       <c r="B39" t="s">
@@ -1190,9 +1314,12 @@
       <c r="D39" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="3">
+      <c r="E39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>6</v>
       </c>
       <c r="B40" t="s">
@@ -1204,9 +1331,12 @@
       <c r="D40" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="3">
+      <c r="E40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>7</v>
       </c>
       <c r="B41" t="s">
@@ -1218,9 +1348,12 @@
       <c r="D41" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="3">
+      <c r="E41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>7</v>
       </c>
       <c r="B42" t="s">
@@ -1232,9 +1365,12 @@
       <c r="D42" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="3">
+      <c r="E42" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>7</v>
       </c>
       <c r="B43" t="s">
@@ -1246,9 +1382,12 @@
       <c r="D43" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
+      <c r="E43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>7</v>
       </c>
       <c r="B44" t="s">
@@ -1260,9 +1399,12 @@
       <c r="D44" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>7</v>
       </c>
       <c r="B45" t="s">
@@ -1274,9 +1416,12 @@
       <c r="D45" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="3">
+      <c r="E45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>7</v>
       </c>
       <c r="B46" t="s">
@@ -1288,9 +1433,12 @@
       <c r="D46" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="3">
+      <c r="E46" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>7</v>
       </c>
       <c r="B47" t="s">
@@ -1302,9 +1450,12 @@
       <c r="D47" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="3">
+      <c r="E47" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>7</v>
       </c>
       <c r="B48" t="s">
@@ -1316,9 +1467,12 @@
       <c r="D48" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="3">
+      <c r="E48" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>7</v>
       </c>
       <c r="B49" t="s">
@@ -1330,9 +1484,12 @@
       <c r="D49" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="3">
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>7</v>
       </c>
       <c r="B50" t="s">
@@ -1344,9 +1501,12 @@
       <c r="D50" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="3">
+      <c r="E50" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
         <v>7</v>
       </c>
       <c r="B51" t="s">
@@ -1358,9 +1518,12 @@
       <c r="D51" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="3">
+      <c r="E51" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>8</v>
       </c>
       <c r="B52" t="s">
@@ -1372,9 +1535,12 @@
       <c r="D52" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="3">
+      <c r="E52" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
         <v>8</v>
       </c>
       <c r="B53" t="s">
@@ -1386,9 +1552,12 @@
       <c r="D53" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="3">
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>8</v>
       </c>
       <c r="B54" t="s">
@@ -1400,9 +1569,12 @@
       <c r="D54" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="3">
+      <c r="E54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
         <v>8</v>
       </c>
       <c r="B55" t="s">
@@ -1414,9 +1586,12 @@
       <c r="D55" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="3">
+      <c r="E55" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
         <v>8</v>
       </c>
       <c r="B56" t="s">
@@ -1428,9 +1603,12 @@
       <c r="D56" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="3">
+      <c r="E56" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
         <v>8</v>
       </c>
       <c r="B57" t="s">
@@ -1442,9 +1620,12 @@
       <c r="D57" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="3">
+      <c r="E57" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
         <v>8</v>
       </c>
       <c r="B58" t="s">
@@ -1456,9 +1637,12 @@
       <c r="D58" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="3">
+      <c r="E58" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
         <v>8</v>
       </c>
       <c r="B59" t="s">
@@ -1470,9 +1654,12 @@
       <c r="D59" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="3">
+      <c r="E59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
         <v>8</v>
       </c>
       <c r="B60" t="s">
@@ -1484,9 +1671,12 @@
       <c r="D60" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="3">
+      <c r="E60" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
         <v>8</v>
       </c>
       <c r="B61" t="s">
@@ -1498,9 +1688,12 @@
       <c r="D61" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="3">
+      <c r="E61" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
         <v>8</v>
       </c>
       <c r="B62" t="s">
@@ -1512,9 +1705,12 @@
       <c r="D62" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="3">
+      <c r="E62" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
         <v>8</v>
       </c>
       <c r="B63" t="s">
@@ -1526,9 +1722,12 @@
       <c r="D63" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="3">
+      <c r="E63" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
         <v>9</v>
       </c>
       <c r="B64" t="s">
@@ -1540,9 +1739,12 @@
       <c r="D64" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
+      <c r="E64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
         <v>9</v>
       </c>
       <c r="B65" t="s">
@@ -1554,9 +1756,12 @@
       <c r="D65" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="3">
+      <c r="E65" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
         <v>9</v>
       </c>
       <c r="B66" t="s">
@@ -1568,9 +1773,12 @@
       <c r="D66" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="3">
+      <c r="E66" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
         <v>9</v>
       </c>
       <c r="B67" t="s">
@@ -1582,9 +1790,12 @@
       <c r="D67" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="3">
+      <c r="E67" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
         <v>9</v>
       </c>
       <c r="B68" t="s">
@@ -1596,9 +1807,12 @@
       <c r="D68" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="3">
+      <c r="E68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
         <v>9</v>
       </c>
       <c r="B69" t="s">
@@ -1610,9 +1824,12 @@
       <c r="D69" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="3">
+      <c r="E69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>9</v>
       </c>
       <c r="B70" t="s">
@@ -1624,9 +1841,12 @@
       <c r="D70" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="3">
+      <c r="E70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
         <v>9</v>
       </c>
       <c r="B71" t="s">
@@ -1638,9 +1858,12 @@
       <c r="D71" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="3">
+      <c r="E71" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>9</v>
       </c>
       <c r="B72" t="s">
@@ -1652,9 +1875,12 @@
       <c r="D72" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="3">
+      <c r="E72" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
         <v>9</v>
       </c>
       <c r="B73" t="s">
@@ -1666,9 +1892,12 @@
       <c r="D73" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="3">
+      <c r="E73" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
         <v>9</v>
       </c>
       <c r="B74" t="s">
@@ -1680,9 +1909,12 @@
       <c r="D74" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="3">
+      <c r="E74" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
         <v>9</v>
       </c>
       <c r="B75" t="s">
@@ -1694,9 +1926,12 @@
       <c r="D75" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="3">
+      <c r="E75" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
         <v>9</v>
       </c>
       <c r="B76" t="s">
@@ -1708,9 +1943,12 @@
       <c r="D76" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="3">
+      <c r="E76" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
         <v>10</v>
       </c>
       <c r="B77" t="s">
@@ -1722,9 +1960,12 @@
       <c r="D77" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="3">
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
         <v>10</v>
       </c>
       <c r="B78" t="s">
@@ -1736,9 +1977,12 @@
       <c r="D78" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="3">
+      <c r="E78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
         <v>10</v>
       </c>
       <c r="B79" t="s">
@@ -1750,9 +1994,12 @@
       <c r="D79" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="3">
+      <c r="E79" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
         <v>10</v>
       </c>
       <c r="B80" t="s">
@@ -1764,9 +2011,12 @@
       <c r="D80" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="3">
+      <c r="E80" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
         <v>10</v>
       </c>
       <c r="B81" t="s">
@@ -1778,9 +2028,12 @@
       <c r="D81" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="3">
+      <c r="E81" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
         <v>10</v>
       </c>
       <c r="B82" t="s">
@@ -1792,9 +2045,12 @@
       <c r="D82" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="3">
+      <c r="E82" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
         <v>10</v>
       </c>
       <c r="B83" t="s">
@@ -1806,9 +2062,12 @@
       <c r="D83" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="3">
+      <c r="E83" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
         <v>10</v>
       </c>
       <c r="B84" t="s">
@@ -1820,9 +2079,12 @@
       <c r="D84" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="3">
+      <c r="E84" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
         <v>10</v>
       </c>
       <c r="B85" t="s">
@@ -1834,9 +2096,12 @@
       <c r="D85" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="3">
+      <c r="E85" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
         <v>10</v>
       </c>
       <c r="B86" t="s">
@@ -1848,9 +2113,12 @@
       <c r="D86" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="3">
+      <c r="E86" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="2">
         <v>10</v>
       </c>
       <c r="B87" t="s">
@@ -1862,9 +2130,12 @@
       <c r="D87" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="3">
+      <c r="E87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
         <v>10</v>
       </c>
       <c r="B88" t="s">
@@ -1876,9 +2147,12 @@
       <c r="D88" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="3">
+      <c r="E88" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" s="2">
         <v>10</v>
       </c>
       <c r="B89" t="s">
@@ -1890,9 +2164,12 @@
       <c r="D89" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="3">
+      <c r="E89" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
         <v>10</v>
       </c>
       <c r="B90" t="s">
@@ -1904,9 +2181,12 @@
       <c r="D90" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="3">
+      <c r="E90" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" s="2">
         <v>10</v>
       </c>
       <c r="B91" t="s">
@@ -1918,9 +2198,12 @@
       <c r="D91" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="3">
+      <c r="E91" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
         <v>10</v>
       </c>
       <c r="B92" t="s">
@@ -1932,9 +2215,12 @@
       <c r="D92" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="3">
+      <c r="E92" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" s="2">
         <v>10</v>
       </c>
       <c r="B93" t="s">
@@ -1946,9 +2232,12 @@
       <c r="D93" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="3">
+      <c r="E93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
         <v>10</v>
       </c>
       <c r="B94" t="s">
@@ -1960,9 +2249,12 @@
       <c r="D94" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="3">
+      <c r="E94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" s="2">
         <v>10</v>
       </c>
       <c r="B95" t="s">
@@ -1974,9 +2266,12 @@
       <c r="D95" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="3">
+      <c r="E95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
         <v>10</v>
       </c>
       <c r="B96" t="s">
@@ -1988,9 +2283,12 @@
       <c r="D96" t="s">
         <v>53</v>
       </c>
+      <c r="E96" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A97" s="3"/>
+      <c r="A97" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
